--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -60,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -75,6 +96,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -90,6 +118,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -105,6 +140,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -120,6 +162,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -135,6 +184,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -147,12 +203,22 @@
       </rPr>
       <t>使用范围</t>
     </r>
+  </si>
+  <si>
+    <t>使用方</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -168,6 +234,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1334,24 +1407,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="20.0909090909091" customWidth="1"/>
-    <col min="3" max="3" width="17.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="20.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="19.725" customWidth="1"/>
+    <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="17.8166666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.0916666666667" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="17.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="20.9090909090909" customWidth="1"/>
-    <col min="9" max="9" width="17.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="15.5454545454545" customWidth="1"/>
-    <col min="11" max="11" width="17.8181818181818" customWidth="1"/>
-    <col min="12" max="12" width="19.7272727272727" customWidth="1"/>
+    <col min="7" max="7" width="17.8166666666667" customWidth="1"/>
+    <col min="8" max="8" width="20.9083333333333" customWidth="1"/>
+    <col min="9" max="10" width="17.725" customWidth="1"/>
+    <col min="11" max="11" width="15.5416666666667" customWidth="1"/>
+    <col min="12" max="12" width="17.8166666666667" customWidth="1"/>
+    <col min="13" max="13" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,14 +1452,17 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>8</v>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,19 @@
     </r>
   </si>
   <si>
-    <t>使用方</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用方</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -1449,7 +1461,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -95,48 +95,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>发货仓库</t>
-    </r>
+    <t>是否需要出库</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>领用人</t>
-    </r>
+    <t>不出库原因</t>
   </si>
   <si>
     <r>
@@ -157,7 +119,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>领用部门</t>
+      <t>发货仓库</t>
     </r>
   </si>
   <si>
@@ -179,7 +141,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>领料组织</t>
+      <t>领用人</t>
     </r>
   </si>
   <si>
@@ -201,11 +163,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>使用范围</t>
+      <t>领用部门</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -216,8 +185,55 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>领料组织</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用范围</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>使用方</t>
     </r>
+  </si>
+  <si>
+    <t>是否需要入台账</t>
   </si>
   <si>
     <t>备注</t>
@@ -265,6 +281,9 @@
       </rPr>
       <t>领用数量</t>
     </r>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
 </sst>
 </file>
@@ -1419,24 +1438,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.725" customWidth="1"/>
     <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
     <col min="3" max="3" width="17.8166666666667" customWidth="1"/>
-    <col min="4" max="4" width="20.0916666666667" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="17.8166666666667" customWidth="1"/>
-    <col min="8" max="8" width="20.9083333333333" customWidth="1"/>
-    <col min="9" max="10" width="17.725" customWidth="1"/>
-    <col min="11" max="11" width="15.5416666666667" customWidth="1"/>
-    <col min="12" max="12" width="17.8166666666667" customWidth="1"/>
-    <col min="13" max="13" width="19.725" customWidth="1"/>
+    <col min="4" max="6" width="20.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="17.8166666666667" customWidth="1"/>
+    <col min="10" max="10" width="20.9083333333333" customWidth="1"/>
+    <col min="11" max="13" width="17.725" customWidth="1"/>
+    <col min="14" max="14" width="15.5416666666667" customWidth="1"/>
+    <col min="15" max="15" width="17.8166666666667" customWidth="1"/>
+    <col min="16" max="16" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1446,10 +1465,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1464,25 +1483,37 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"办公领用,拍摄,研发,抖音直播,客服领用（客户指导使用）,参展,营销样品,认证检测,供应链生产组装,用户新品体验（仓库提供）,不良品分析（从售后仓领样）,星河线下领用,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576 L$1:L$1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
       <formula1>"公司内部使用,公司外部使用"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -120,6 +120,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>发货仓库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>用途说明</t>
     </r>
   </si>
   <si>
@@ -296,7 +310,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +467,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1438,24 +1458,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.725" customWidth="1"/>
     <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
     <col min="3" max="3" width="17.8166666666667" customWidth="1"/>
     <col min="4" max="6" width="20.0916666666667" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="17.8166666666667" customWidth="1"/>
-    <col min="10" max="10" width="20.9083333333333" customWidth="1"/>
-    <col min="11" max="13" width="17.725" customWidth="1"/>
-    <col min="14" max="14" width="15.5416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.8166666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.725" customWidth="1"/>
+    <col min="7" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="17.8166666666667" customWidth="1"/>
+    <col min="11" max="11" width="20.9083333333333" customWidth="1"/>
+    <col min="12" max="14" width="17.725" customWidth="1"/>
+    <col min="15" max="15" width="15.5416666666667" customWidth="1"/>
+    <col min="16" max="16" width="17.8166666666667" customWidth="1"/>
+    <col min="17" max="17" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1489,20 +1509,23 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1510,10 +1533,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"办公领用,拍摄,研发,抖音直播,客服领用（客户指导使用）,参展,营销样品,认证检测,供应链生产组装,用户新品体验（仓库提供）,不良品分析（从售后仓领样）,星河线下领用,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576 L$1:L$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576 M$1:M$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>"公司内部使用,公司外部使用"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleRecipientTemplate.xlsx
@@ -124,6 +124,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1531,7 +1538,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
-      <formula1>"办公领用,拍摄,研发,抖音直播,客服领用（客户指导使用）,参展,营销样品,认证检测,供应链生产组装,用户新品体验（仓库提供）,不良品分析（从售后仓领样）,星河线下领用,其他"</formula1>
+      <formula1>"办公领用,拍摄,研发,抖音直播,客服领用（客户指导使用）,参展,营销样品,认证检测,供应链生产组装,用户新品体验（仓库提供）,不良品分析（从售后仓领样）,星河线下领用,其他,员工福利"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576 M$1:M$1048576">
       <formula1>"是,否"</formula1>
